--- a/results/final_model_comparison.xlsx
+++ b/results/final_model_comparison.xlsx
@@ -460,138 +460,138 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>0.9925</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.99</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>0.9925</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9875</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.99</v>
       </c>
       <c r="F2" t="n">
         <v>0.9996</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0846</v>
+        <v>3.828</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9423</v>
+        <v>0.9875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9499</v>
+        <v>0.9899</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9338</v>
+        <v>0.985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9418</v>
+        <v>0.9875</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9799</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>0.9992</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.5315</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-SVM</t>
+          <t>Autoencoder</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9421</v>
+        <v>0.97</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9528</v>
+        <v>0.9498</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9303</v>
+        <v>0.9925</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9414</v>
+        <v>0.9707</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9789</v>
+        <v>0.9981</v>
       </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.9423</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9338</v>
+      </c>
+      <c r="E5" t="n">
         <v>0.9418</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.9503</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9323</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9412</v>
-      </c>
       <c r="F5" t="n">
-        <v>0.9804</v>
+        <v>0.9799</v>
       </c>
       <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>TC-SVM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7312</v>
+        <v>0.9421</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7548</v>
+        <v>0.9528</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.9303</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.9414</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7859</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.4745</v>
-      </c>
+        <v>0.9789</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Autoencoder</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.55</v>
+        <v>0.9418</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9503</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1</v>
+        <v>0.9323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1818</v>
+        <v>0.9412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9944</v>
+        <v>0.9804</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
